--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="110">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -256,10 +256,7 @@
 </t>
   </si>
   <si>
-    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
-  </si>
-  <si>
-    <t>Synonyme : secteurConventionnement</t>
+    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie (Synonyme : secteurConventionnement).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -341,16 +338,13 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
+    <t>Liste des conventionnements CNAM.</t>
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>required</t>
-  </si>
-  <si>
-    <t>Liste des conventionnement CNAM.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J130-CNAMAmeliSecteurConventionnement-RASS/FHIR/JDV-J130-CNAMAmeliSecteurConventionnement-RASS</t>
@@ -694,7 +688,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="33.703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="135.0390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -857,9 +851,7 @@
       <c r="M2" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="N2" t="s" s="2">
-        <v>81</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>76</v>
@@ -917,10 +909,10 @@
         <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>76</v>
@@ -928,10 +920,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -942,25 +934,25 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1011,13 +1003,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1026,15 +1018,15 @@
         <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1057,13 +1049,13 @@
         <v>76</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1102,19 +1094,19 @@
         <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
@@ -1123,10 +1115,10 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -1134,10 +1126,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1145,10 +1137,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
@@ -1160,16 +1152,16 @@
         <v>76</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1219,13 +1211,13 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
@@ -1234,15 +1226,15 @@
         <v>76</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1253,7 +1245,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -1265,13 +1257,13 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1298,14 +1290,12 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>110</v>
-      </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
       </c>
@@ -1322,22 +1312,22 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1115,7 +1115,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
@@ -1321,7 +1321,7 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>109</v>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1115,7 +1115,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
@@ -1321,7 +1321,7 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>109</v>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1115,7 +1115,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
@@ -1321,7 +1321,7 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>109</v>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1115,7 +1115,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
@@ -1321,7 +1321,7 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>109</v>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/main/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
